--- a/input/reg_childcarecost.xlsx
+++ b/input/reg_childcarecost.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyFiles\99 DEV ENV\JAS-MINE\SimPaths\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sonnewald/GitHub/SimPaths/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A202D41-1A3C-4889-8F9C-F2FF196DE166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FD3F876-92F3-8D40-A8D0-8CCCEEAF3941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{340E7E3D-052B-4B5E-9AED-F19FDC9FFE2D}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17820" activeTab="2" xr2:uid="{340E7E3D-052B-4B5E-9AED-F19FDC9FFE2D}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
-    <sheet name="UK_C1a" sheetId="2" r:id="rId2"/>
-    <sheet name="UK_C1b" sheetId="3" r:id="rId3"/>
+    <sheet name="C1a" sheetId="2" r:id="rId2"/>
+    <sheet name="C1b" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -554,17 +554,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02DCC908-06A0-4D0E-870F-9C33F376D6B8}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="1" max="1" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -572,7 +572,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -580,7 +580,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -588,7 +588,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>48</v>
       </c>
@@ -596,7 +596,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>44</v>
       </c>
@@ -604,7 +604,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -620,12 +620,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B3F6B67-F044-4186-B2FF-5ED7C0833841}">
   <dimension ref="A1:AL37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="29.7109375" customWidth="1"/>
+    <col min="1" max="1" width="29.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -741,7 +741,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -857,7 +857,7 @@
         <v>-1.1940501274252439E-4</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -973,7 +973,7 @@
         <v>-3.1038219177078686E-4</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1089,7 +1089,7 @@
         <v>-3.2025663874226084E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1205,7 +1205,7 @@
         <v>-2.6884268111430698E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1321,7 +1321,7 @@
         <v>-2.3192061522138812E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1437,7 +1437,7 @@
         <v>-1.8977642800305613E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -1553,7 +1553,7 @@
         <v>-1.7706423552610345E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -1669,7 +1669,7 @@
         <v>-1.7318200000436841E-4</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -1785,7 +1785,7 @@
         <v>-1.3751330765226783E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -1901,7 +1901,7 @@
         <v>-1.8070224025607372E-4</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>-1.2786569768535543E-4</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -2133,7 +2133,7 @@
         <v>-2.0532987640655039E-4</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -2249,7 +2249,7 @@
         <v>-2.1777547755614897E-4</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>-2.5991293895444572E-4</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>-2.7214011717062285E-4</v>
       </c>
     </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>36</v>
       </c>
@@ -2597,7 +2597,7 @@
         <v>-8.1276516587627974E-4</v>
       </c>
     </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -2713,7 +2713,7 @@
         <v>-7.4381556535704817E-4</v>
       </c>
     </row>
-    <row r="19" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -2829,7 +2829,7 @@
         <v>-7.4366693370203759E-4</v>
       </c>
     </row>
-    <row r="20" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>39</v>
       </c>
@@ -2945,7 +2945,7 @@
         <v>-7.2710280334744367E-4</v>
       </c>
     </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -3061,7 +3061,7 @@
         <v>-7.6818679487808687E-4</v>
       </c>
     </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>41</v>
       </c>
@@ -3177,7 +3177,7 @@
         <v>-7.0149132813932002E-4</v>
       </c>
     </row>
-    <row r="23" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>42</v>
       </c>
@@ -3293,7 +3293,7 @@
         <v>-7.6916905904389694E-4</v>
       </c>
     </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>43</v>
       </c>
@@ -3409,7 +3409,7 @@
         <v>-8.548302750787998E-4</v>
       </c>
     </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -3525,7 +3525,7 @@
         <v>-8.572859223045347E-5</v>
       </c>
     </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -3641,7 +3641,7 @@
         <v>-6.0495484615649057E-4</v>
       </c>
     </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -3757,7 +3757,7 @@
         <v>-6.0358934633460517E-4</v>
       </c>
     </row>
-    <row r="28" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -3873,7 +3873,7 @@
         <v>-5.9927099771446004E-4</v>
       </c>
     </row>
-    <row r="29" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -3989,7 +3989,7 @@
         <v>-5.8816896403483473E-4</v>
       </c>
     </row>
-    <row r="30" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -4105,7 +4105,7 @@
         <v>-5.8978413486622354E-4</v>
       </c>
     </row>
-    <row r="31" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -4221,7 +4221,7 @@
         <v>-5.9036287177352976E-4</v>
       </c>
     </row>
-    <row r="32" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -4337,7 +4337,7 @@
         <v>-5.6509859437920491E-4</v>
       </c>
     </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>31</v>
       </c>
@@ -4453,7 +4453,7 @@
         <v>-5.8242336098999082E-4</v>
       </c>
     </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -4569,7 +4569,7 @@
         <v>-5.5137552841517186E-4</v>
       </c>
     </row>
-    <row r="35" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -4685,7 +4685,7 @@
         <v>-5.9512024002572172E-4</v>
       </c>
     </row>
-    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -4801,7 +4801,7 @@
         <v>-5.7550474295670333E-4</v>
       </c>
     </row>
-    <row r="37" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -4925,12 +4925,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B1C2FB7-24E7-4EED-B8B4-6BEC3D4AEE9C}">
   <dimension ref="A1:AL37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="29.7109375" customWidth="1"/>
+    <col min="1" max="1" width="29.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -5046,7 +5046,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -5162,7 +5162,7 @@
         <v>-1.0988840707260321E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -5278,7 +5278,7 @@
         <v>-2.0860678616377998E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -5394,7 +5394,7 @@
         <v>-2.0754189833965863E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -5510,7 +5510,7 @@
         <v>-1.3659410574471591E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -5626,7 +5626,7 @@
         <v>-1.5322588259952688E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -5742,7 +5742,7 @@
         <v>-1.5174772951368979E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -5858,7 +5858,7 @@
         <v>-1.6240689961370923E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -5974,7 +5974,7 @@
         <v>-1.627399088708391E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -6090,7 +6090,7 @@
         <v>6.1375832303350657E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -6206,7 +6206,7 @@
         <v>-1.3531113112763848E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -6322,7 +6322,7 @@
         <v>-1.3308391974300715E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -6438,7 +6438,7 @@
         <v>-1.4175362768765209E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -6554,7 +6554,7 @@
         <v>-1.0687492043537587E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -6670,7 +6670,7 @@
         <v>-1.3343520888660326E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -6786,7 +6786,7 @@
         <v>-1.4086874585459387E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>36</v>
       </c>
@@ -6902,7 +6902,7 @@
         <v>-6.9708180270447208E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -7018,7 +7018,7 @@
         <v>-6.0976037477587898E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -7134,7 +7134,7 @@
         <v>-6.6807141687624952E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>39</v>
       </c>
@@ -7250,7 +7250,7 @@
         <v>-6.6618656169871145E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -7366,7 +7366,7 @@
         <v>-4.4500421694721598E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>41</v>
       </c>
@@ -7482,7 +7482,7 @@
         <v>-6.343457515299745E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>42</v>
       </c>
@@ -7598,7 +7598,7 @@
         <v>-7.4640299292123074E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>43</v>
       </c>
@@ -7714,7 +7714,7 @@
         <v>-7.5125146673039565E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -7830,7 +7830,7 @@
         <v>-1.0086295438412555E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -7946,7 +7946,7 @@
         <v>-4.9456247933747435E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -8062,7 +8062,7 @@
         <v>-4.7881410340712919E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -8178,7 +8178,7 @@
         <v>-4.9256089086976672E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -8294,7 +8294,7 @@
         <v>-4.7563857145477067E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -8410,7 +8410,7 @@
         <v>-4.9452335674630915E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -8526,7 +8526,7 @@
         <v>-4.6931900901194786E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -8642,7 +8642,7 @@
         <v>-4.6965114607928765E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>31</v>
       </c>
@@ -8758,7 +8758,7 @@
         <v>-4.5816250454203226E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -8874,7 +8874,7 @@
         <v>-4.2959609726974718E-3</v>
       </c>
     </row>
-    <row r="35" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -8990,7 +8990,7 @@
         <v>-4.9216305072843454E-3</v>
       </c>
     </row>
-    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -9106,7 +9106,7 @@
         <v>-4.6945043529770109E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>35</v>
       </c>
